--- a/Doc/Unit_Test_Plan_v0.1_CoachAI_Completed.xlsx
+++ b/Doc/Unit_Test_Plan_v0.1_CoachAI_Completed.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Unit Test Plan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Unit Test Plan'!$A$5:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Unit Test Plan'!$A$5:$F$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -65,7 +65,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00006100"/>
-      <sz val="9"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -79,18 +79,12 @@
       <sz val="7"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -100,8 +94,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -165,27 +159,27 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -193,7 +187,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -565,8 +559,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -574,21 +568,19 @@
     <col width="38" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoachAI — Unit Test Plan v0.1 (AI Customer Support Assistant with Live Response Guidance)</t>
+          <t>CoachAI - Unit Test Plan v0.1 (AI Customer Support Assistant with Live Response Guidance)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Test Plan covers 28 test cases across Agents, RAG, LLM chain, APIs, Frontend &amp; Integrations | Execution: pytest + vitest + node --test | Entry criteria: code committed to final/main | Exit criteria: 100% Pass | Date: 27-Aug-2026 | Tester: QA Team (CoachAI)</t>
+          <t>Test Plan covers 28 test cases across Agents, RAG, LLM chain, APIs, Frontend and Integrations | Execution: pytest + vitest + node --test | Entry: code committed to final/main | Exit: 100% Pass | Date: 27-Aug-2026 | Tester: QA Team</t>
         </is>
       </c>
     </row>
@@ -598,7 +590,7 @@
     <row r="4" ht="14" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Project: Development of AI-Powered Customer Support Assistant with Live Response Guidance  •  Module: Multi-Agent System (25 agents) + RAG + Full-Stack (React/Node/Python/Postgres)  •  Environment: Windows 11, Node 18+, Python 3.11, Postgres (Neon) / SQLite fallback, Azure OpenAI + OpenRouter + Groq</t>
+          <t>Project: Development of AI-Powered Customer Support Assistant with Live Response Guidance | Module: Multi-Agent System (25 agents) + RAG + Full-Stack (React/Node/Python/Postgres) | Env: Windows 11, Node 18+, Python 3.11, Postgres (Neon)/SQLite fallback, Azure OpenAI + OpenRouter + Groq</t>
         </is>
       </c>
     </row>
@@ -631,16 +623,6 @@
       <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Remarks / Test Data</t>
         </is>
       </c>
     </row>
@@ -662,27 +644,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Agent returns valid intent, sentiment, frustration 0-1 &amp; trend -1..1; LLM JSON parsed via regex fallback if needed</t>
+          <t>Agent returns valid intent, sentiment, frustration 0-1 and trend -1..1; JSON parsed via regex fallback if needed</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>intent='order_delay' (or closest enum), sentiment='negative', frustration ≥0.6, trend ≤0</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>intent='order_delay', sentiment='negative', frustration=0.72, trend=-0.4 — parsed correctly (fallback not needed)</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Valid intents enum injected; temp 0.1; fallback verified by forcing markdown fence</t>
+          <t>intent='order_delay', sentiment='negative', frustration &gt;=0.6, trend &lt;=0</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>PASS - intent='order_delay', sentiment='negative', frustration=0.72, trend=-0.4 - parsed correctly</t>
         </is>
       </c>
     </row>
@@ -708,22 +680,12 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>risk ≥0.65, level='high', strategy='offer immediate resolution &amp; manager alert'</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>risk=0.71, level='high', strategy='Immediate manager takeover suggested' — matches expected</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>Covered in test_agents.py; 6 rule scenarios</t>
+          <t>risk &gt;=0.65, level='high', strategy='offer immediate resolution and manager alert'</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>PASS - risk=0.71, level='high', strategy='Immediate manager takeover suggested'</t>
         </is>
       </c>
     </row>
@@ -733,43 +695,33 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>TC-RAG-03: Ingestion Multi-Format &amp; Chunking</t>
+          <t>TC-RAG-03: Ingestion Multi-Format and Chunking</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
           <t>1. Place .txt/.pdf/.docx/.json/.md/.csv/.html in data/knowledge_base/
 2. Call ingest_directory()
-3. Assert chunk length ≤512 &amp; oversized re-split by sentence</t>
+3. Assert chunk &lt;=512 and re-split by sentence</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>All 7 formats parsed, paragraph split → ≤512 chunks, no chunk exceeds limit; PyPDF2 used for PDF</t>
+          <t>All 7 formats parsed, paragraph split -&gt; &lt;=512 chunks, no chunk exceeds limit</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>19 FAQ JSON ingested, chunks=47, max_len=498, pdf 'refund_policy.pdf' parsed 5 chunks</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>47 chunks, max 498 chars, all formats ingested correctly</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Test data: data/knowledge_base/19 FAQs + sample.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
+          <t>19 FAQ JSON ingested, chunks=47, max_len=498, pdf parsed 5 chunks</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>PASS - 47 chunks, max 498 chars, all formats ingested</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="9" t="n">
         <v>4</v>
       </c>
@@ -780,34 +732,24 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>1. With OPENROUTER_API_KEY → query 'refund UPI payment failed'
-2. Without key (offline) repeat query
+          <t>1. With OPENROUTER_API_KEY query 'refund UPI payment failed'
+2. Without key repeat query
 3. Compare top result</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Semantic path (cosine, 2048d nemotron) returns when key present; offline always returns via BM25/keyword overlap, never empty</t>
+          <t>Semantic path (cosine 2048d nemotron) returns when key present; offline always returns via BM25, never empty</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>With key: semantic top 'upi_refund_faq' relevance 0.82; Without key: keyword top same doc relevance 0.61</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>With key 0.82 (semantic), without key 0.61 (keyword) — both non-empty, correct doc</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>test_rag.py::test_hybrid_retrieval; offline fallback critical for demo</t>
+          <t>With key: semantic top 'upi_refund_faq' relevance 0.82; Without key: keyword top same doc 0.61</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>PASS - With key 0.82 (semantic), without key 0.61 (keyword) - both non-empty</t>
         </is>
       </c>
     </row>
@@ -817,39 +759,29 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>TC-RAG-05: KB-Gap Detection &amp; Auto-KB Draft</t>
+          <t>TC-RAG-05: KB-Gap Detection and Auto-KB Draft</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>1. Query 'What is the CEO's personal phone?' (out-of-KB)
+          <t>1. Query 'What is CEO personal phone?' (out-of-KB)
 2. Call knowledge_recommendation.recommend()
-3. Check relevance &amp; pending file</t>
+3. Check relevance and pending file</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Relevance &lt;0.45 → '⚠️ Knowledge Base Gap' item + pending/faq_auto_gen_*.json drafted with heuristic FAQ</t>
+          <t>Relevance &lt;0.45 -&gt; 'Knowledge Base Gap' item + pending/faq_auto_gen_*.json drafted</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Gap alert shown, pending file faq_auto_gen_20260822.json created with draft Q&amp;A</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>Gap alert triggered (relevance 0.21), pending file created, content plausible</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Verified pending/ dir auto-creates; human review required before promote</t>
+          <t>Gap alert shown, pending file faq_auto_gen_20260822.json created</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>PASS - Gap alert trigger relevance 0.21, pending file created</t>
         </is>
       </c>
     </row>
@@ -871,31 +803,21 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Single LLM call returns {csat, churn, viral, fraud, defection, monologue, escalation_trigger, pr_statement} with heuristic fallback on empty</t>
+          <t>Single LLM call returns {csat, churn, viral, fraud, defection, monologue, escalation_trigger, pr_statement}</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>CSAT 2, churn 68%, viral 'high - twitter threat', fraud low, defection 'Swiggy' + counter 'STAY15', monologue non-empty</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>All 8 keys present, CSAT 2/churn 68% plausible, fallback dict used when LLM empty</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Prompt size optimized; dict contract tested vs Pydantic model discussion</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
+          <t>CSAT 2, churn 68%, viral 'high - twitter', fraud low, defection 'Swiggy' + counter 'STAY15'</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>PASS - All 8 keys present, CSAT 2/churn 68% plausible</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>7</v>
       </c>
@@ -906,14 +828,14 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>1. Provide intent + KB tip + conversation context
+          <t>1. Provide intent + KB tip + context
 2. Call coaching_suggestion.analyze_response()
-3. Inspect reply, tone, clarity 1-5, suggested_actions</t>
+3. Inspect reply, tone, clarity 1-5</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Returns CoachingFeedback with reply ≤300 chars, tone in (empathetic, formal, apologetic), clarity 1-5, key_point non-empty</t>
+          <t>Returns CoachingFeedback with reply &lt;=300 chars, tone in (empathetic, formal), clarity 1-5</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -921,19 +843,9 @@
           <t>Reply='I sincerely apologize...' tone='empathetic' clarity=4 actions=['apologize','offer refund']</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>Reply valid, tone empathetic, clarity 4 — meets contract</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Macros library injected; retention-code nudges verified</t>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>PASS - Reply valid, tone empathetic, clarity 4</t>
         </is>
       </c>
     </row>
@@ -955,27 +867,17 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>overall = resolution×0.5 + coaching×0.3 + clarity/CSAT×0.2, sentiment journey length = turns, knowledge_gaps listed</t>
+          <t>overall = resolution*0.5 + coaching*0.3 + clarity/CSAT*0.2, journey length = turns, gaps listed</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>overall=0.78, journey 5 points, gaps 1 (payment), coaching_tips 3</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>overall 0.78 matches manual calc, journey correct</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>Hall of Fame threshold ≥0.85, Shame ≤0.45 verified separately</t>
+          <t>overall=0.78, journey 5 points, gaps 1, tips 3</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>PASS - overall 0.78 matches manual calc</t>
         </is>
       </c>
     </row>
@@ -985,7 +887,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>TC-LLM-09: LLM Chain Fallback (Azure→OpenRouter→Groq)</t>
+          <t>TC-LLM-09: LLM Chain Fallback (Azure-&gt;OpenRouter-&gt;Groq)</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -998,27 +900,17 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Azure primary when set else race OpenRouter vs Groq (2 threads) first winner; empty string → heuristic path; never crashes</t>
+          <t>Azure primary when set else race OpenRouter vs Groq first winner; empty -&gt; heuristic path; never crashes</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Groq-only → llama3 response; Azure-only → gpt response; no-key → '' then heuristic fallback in agent</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Azure hit 1st when present (120ms), Groq fallback 340ms, no-key degraded correctly</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>llm.py / llm.js mirrored; tested via mock keys</t>
+          <t>Groq-only -&gt; llama3 response; Azure-only -&gt; gpt response; no-key -&gt; '' then heuristic</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>PASS - Azure hit 1st when present (120ms), Groq fallback 340ms, no-key degraded</t>
         </is>
       </c>
     </row>
@@ -1034,33 +926,22 @@
       <c r="C15" s="10" t="inlineStr">
         <is>
           <t>1. Call manager_supervisor with frustration 0.3
-2. Again with 0.7
-3. Inspect ManagerIntervention</t>
+2. Again with 0.7</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>No-op (intervene=False) unless frustration≥0.5 or escalation≥0.5; when intervenes, scripted takeover statement non-empty</t>
+          <t>No-op (intervene=False) unless frustration&gt;=0.5 or escalation&gt;=0.5; when intervenes, scripted takeover non-empty</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>0.3 → no-op; 0.7 → intervene True + 'As supervisor...' takeover draft</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>Threshold behavior correct; fast-path saves latency on calm turns</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>Calibrator threshold 0.5-0.8 adaptive — separate test</t>
+          <t>0.3 -&gt; no-op; 0.7 -&gt; intervene True + 'As supervisor...' draft</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>PASS - Threshold behavior correct</t>
         </is>
       </c>
     </row>
@@ -1076,32 +957,22 @@
       <c r="C16" s="7" t="inlineStr">
         <is>
           <t>1. Call tone_rewriter.rewrite('ok')
-2. Call with 'Your refund will be processed in 5 days but...' (normal)</t>
+2. Call with 'Your refund will be processed in 5 days...'</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>len&lt;10 → canned apology empathy reply (not verbatim); normal → polished empathetic rewrite, retains meaning</t>
+          <t>len&lt;10 -&gt; canned apology (not verbatim); normal -&gt; polished empathetic rewrite</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>'ok' → 'I understand your concern...' canned; long draft → polished empathetic version</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>'ok' returned canned apology, long draft polished correctly</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Rate-limit guard documented in defect #6</t>
+          <t>'ok' -&gt; 'I understand your concern...' canned; long draft -&gt; polished version</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>PASS - 'ok' returned canned apology, long polished correctly</t>
         </is>
       </c>
     </row>
@@ -1111,38 +982,28 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>TC-AUTO-12: Auto-KB &amp; Auto-Pilot Actions</t>
+          <t>TC-AUTO-12: Auto-KB and Auto-Pilot Actions</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>1. Trigger KB gap → auto_kb_agent draft
-2. Call auto_pilot_agent on 'refund ₹250' request</t>
+          <t>1. Trigger KB gap -&gt; auto_kb_agent draft
+2. Call auto_pilot_agent on 'refund Rs.250'</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Auto-KB writes pending JSON; Auto-Pilot returns AutoPilotResult with reply + tool action (process_refund/grant_voucher) + optional Composio email</t>
+          <t>Auto-KB writes pending JSON; Auto-Pilot returns reply + tool action (refund/voucher) + optional Composio email</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>Pending file exists; autopilot reply='Refund initiated...' action='process_refund' tool succeeded (mock)</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>Both agents file/action succeeded; with COMPOSIO flag, email draft logged</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>Tool mock rejects &gt;₹500 without supervisor — tested</t>
+          <t>Pending file exists; autopilot reply='Refund initiated...' action='process_refund'</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>PASS - Both file/action succeeded</t>
         </is>
       </c>
     </row>
@@ -1163,27 +1024,17 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>With key: JIRA_CREATE_ISSUE creates ticket in COMPOSIO_JIRA_PROJECT_KEY; without key → failed ToolCallResult with message, no crash, mock ticket shown</t>
+          <t>With key: JIRA_CREATE_ISSUE creates ticket; without key -&gt; failed ToolCallResult with message, no crash</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>With key mock: ticket COACH-123 created; Without key: 'Composio not configured' msg, mock ticket still rendered</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>With/without key both handled, UI shows appropriate toast</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Endpoint also tested via frontend JiraBoard</t>
+          <t>With key mock: COACH-123 created; Without key: 'Composio not configured' mock shown</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>PASS - Both handled, UI toast appropriate</t>
         </is>
       </c>
     </row>
@@ -1205,27 +1056,17 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Keyword pre-scan seeds defaults; LLM refines; each returns RiskResult with level, probability, protocol/counter-offer</t>
+          <t>Keyword pre-scan seeds defaults; LLM refines; each returns RiskResult with level/probability/protocol</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>Viral high (twitter), fraud high (abuse) + protocol, defection 'Swiggy' + 'STAY15' offer</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>All three detectors returned seeded + LLM-refined results</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>Pre-scan lists include Hinglish variants like 'paise wapas'</t>
+          <t>Viral high (twitter), fraud high + protocol, defection 'Swiggy' + 'STAY15'</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>PASS - All three returned seeded+LLM results</t>
         </is>
       </c>
     </row>
@@ -1235,38 +1076,28 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>TC-MIND-15: Mind Reader &amp; Multiverse Simulator</t>
+          <t>TC-MIND-15: Mind Reader and Multiverse</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
           <t>1. Call mind_reader on angry msg
-2. Call multiverse_simulator with same context</t>
+2. Call multiverse_simulator</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Mind Reader returns internal monologue string; Multiverse returns 2-3 branches each with reply variant + predicted CSAT</t>
+          <t>Mind Reader returns monologue; Multiverse returns 2-3 branches each with reply variant + predicted CSAT</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Monologue='This is the 3rd time...' ; Branches: empathetic CSAT 4.2 vs rigid 2.1</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Monologue + 2 branches returned, CSAT predictions differ meaningfully</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>Temperature 0.5 for creativity; shown in Feature Lab</t>
+          <t>Monologue='This is 3rd time...' ; Branches: empathetic 4.2 vs rigid 2.1</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>PASS - Monologue + 2 branches returned, CSAT differ</t>
         </is>
       </c>
     </row>
@@ -1282,73 +1113,53 @@
       <c r="C21" s="10" t="inlineStr">
         <is>
           <t>1. Build report overall 0.82
-2. Call qa_audit_agent + cognitive_load + patience_clock</t>
+2. Call qa_audit + cognitive_load + patience_clock</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>QA audit pass if overall≥0.75 (21 ISO checks); cognitive load bucket on frustration+words; patience est turns-until-dropoff</t>
+          <t>QA pass if overall&gt;=0.75 (21 checks); cognitive bucket on frustration+words; patience est turns-until-dropoff</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>QA PASS (18/21), cognitive 'medium load', patience '2 turns left' on high frustration</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>QA PASS correctly, load/patience heuristics match spec</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>Auditor used in report_page QA card</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
+          <t>QA PASS (18/21), cognitive 'medium load', patience '2 turns left'</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>PASS - QA PASS correct, load/patience match spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="6" t="n">
         <v>17</v>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>TC-SESSION-17: Session Start &amp; Per-Turn &lt;0.5s</t>
+          <t>TC-SESSION-17: Session Start and Per-Turn Latency</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>1. POST /api/session/start {mode:'simulator', agent_name:'Test'}
-2. POST /api/chat/message (customer msg) measure latency</t>
+          <t>1. POST /api/session/start {mode:'simulator'}
+2. POST /api/chat/message measure latency</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Session id returned + initial customer msg in simulator+fast mode; per-turn latency target &lt;500ms for intent+rag+coaching pipeline</t>
+          <t>Session id + initial customer msg in simulator+fast mode; per-turn latency target &lt;500ms</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>sessionId abc123, first msg 'My order...', turn latency 380ms (p50) 620ms (p95) — within SLA</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Session started, latency 380ms avg, meets &lt;0.5s p50</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Load test 50 concurrent → p95 780ms tolerable due to LLM</t>
+          <t>sessionId abc123, first msg 'My order...', turn 380ms (p50) 620ms (p95)</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>PASS - Session started, latency 380ms avg, meets &lt;0.5s p50</t>
         </is>
       </c>
     </row>
@@ -1358,39 +1169,29 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>TC-AUTH-18: Auth Register/Login/Guest &amp; Password Guard</t>
+          <t>TC-AUTH-18: Auth Register/Login/Guest and Password Guard</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>1. POST /api/auth/register {name,email,pass='123'}
+          <t>1. POST /api/auth/register {pass='123'}
 2. Repeat pass='password123'
 3. POST /api/auth/guest</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Short password (&lt;6) → 400 'password too short'; valid → user+token; guest → instant demo account + token; GET /api/auth/me verifies</t>
+          <t>Short password (&lt;6) -&gt; 400; valid -&gt; user+token; guest -&gt; demo account + token; GET /api/auth/me</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>123 → 400 error; valid → 201+token; guest → 200+token; /me returns current user</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>Auth guards correct; bearer token flow works</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>Token stored in localStorage, api.js attaches Authorization header</t>
+          <t>123 -&gt; 400 error; valid -&gt; 201+token; guest -&gt; 200+token; /me returns user</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>PASS - Auth guards correct; bearer flow works</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1201,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>TC-API-19: Coaching Turn &amp; Manager Takeover Endpoints</t>
+          <t>TC-API-19: Coaching Turn and Manager Takeover</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1412,69 +1213,49 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Chat/message returns coachTurn (signals, KB, reply, risk flat fields); manager-takeover injects supervisor msg; chat/end builds &amp; saves report + hall-of-fame check</t>
+          <t>chat/message returns coachTurn (signals, KB, reply, risk flat fields); takeover injects msg; chat/end builds report</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>coachTurn JSON correct (sentiment, frustration, tip, escalation); takeover msg injected; report overall 0.81 saved</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>All three endpoints returned expected JSON &amp; DB persisted</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>Verified _serialize_turn flattening matches frontend expectations</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
+          <t>coachTurn JSON correct; takeover injected; report overall 0.81 saved</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>PASS - All endpoints returned expected JSON and DB persisted</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="9" t="n">
         <v>20</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>TC-DB-20: Persistence &amp; Rehydration (Cold Start)</t>
+          <t>TC-DB-20: Persistence and Rehydration (Cold Start)</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>1. Start session, add 3 turns, note sessionId
-2. Simulate cold start: clear in-memory _sessions
-3. GET session via bind_session / chat/message</t>
+          <t>1. Start session, add 3 turns
+2. Simulate cold start: clear _sessions
+3. GET session via bind_session</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Full SessionState rehydrated from pg coach_sessions.full_state JSON; messages+turn_analyses preserved across instances</t>
+          <t>Full SessionState rehydrated from pg coach_sessions.full_state JSON; messages+turn_analyses preserved</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>After clear, getSession rehydrated 3 turns intact, next message appends as 4th</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>Rehydration succeeded, Vercel cold-start bug fixed (defect #8)</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>DB table coil: sessions(config, messages, full_state, is_active)</t>
+          <t>After clear, getSession rehydrated 3 turns intact, next message 4th</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>PASS - Rehydration succeeded, cold-start bug fixed</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1265,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>TC-REPORT-21: Reports, Analytics &amp; Hall of Fame APIs</t>
+          <t>TC-REPORT-21: Reports, Analytics and Hall of Fame</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1496,27 +1277,17 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Reports from DB (not fs) array with overall_score; analytics {live, completed, avg}; hall-of-fame partitioned ≥0.85/≤0.45</t>
+          <t>Reports from DB (not fs) array with overall_score; analytics {live, completed, avg}; hall-of-fame partitioned &gt;=0.85/&lt;=0.45</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>reports=42, avg 86, live 2, hall fame 7, shame 3 — all from DB</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>APIs returned DB-authoritative data, fs never read on Vercel</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>Ephemeral FS defect #9 regression covered</t>
+          <t>reports=42, avg 86, live 2, hall fame 7, shame 3 - all from DB</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>PASS - APIs returned DB-authoritative data</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1297,7 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>TC-RAG-API-22: Knowledge &amp; Search Debugger + Cache Reset</t>
+          <t>TC-RAG-API-22: Knowledge and Search Debugger</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -1538,27 +1309,17 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Knowledge lists 19 docs; scenario generator returns GeneratedScenario with difficulty; cache/reset clears embedding cache</t>
+          <t>Knowledge lists 19 docs; scenario generator returns GeneratedScenario; cache/reset clears cache</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>knowledge 19 items, scenario 'UPI failure' difficulty 'medium' generated, cache reset {ok:true}</t>
-        </is>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>All RAG admin endpoints functional</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>KB admin tabs: search debugger, index document, chunk simulator tested manually</t>
+          <t>knowledge 19 items, scenario 'UPI failure' medium generated, cache reset {ok:true}</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>PASS - All RAG admin endpoints functional</t>
         </is>
       </c>
     </row>
@@ -1568,38 +1329,28 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>TC-INT-23: Analytics Frontend &amp; Export (jsPDF/csv)</t>
+          <t>TC-INT-23: Analytics Frontend and Export</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>1. Open Analytics page, verify TanStack Query loads
-2. Click Export PDF &amp; CSV on Reports page</t>
+          <t>1. Open Analytics page, verify Query loads
+2. Click Export PDF and CSV on Reports</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Analytics shows live sessions, leaderboard, trends; PDF export generates via jsPDF + autotable, CSV via blob download</t>
+          <t>Analytics shows live sessions, leaderboard, trends; PDF via jsPDF + autotable, CSV via blob</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Analytics rendered, PDF 42 reports exported (2 pages), CSV downloaded 15KB</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>Frontend analytics &amp; export working, vitest covers</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>vitest suite: 7 tests incl. CSV/PDF export</t>
+          <t>Analytics rendered, PDF 42 reports 2 pages, CSV 15KB</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>PASS - Frontend analytics and export working</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1360,7 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>TC-DEPLOY-24: Health Check &amp; Build</t>
+          <t>TC-DEPLOY-24: Health Check and Build</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -1621,7 +1372,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Health returns {status:'online', engine, rag, db:bool, vector_store}; vite build succeeds (route split 58% saving); Vercel deploy green</t>
+          <t>Health returns {status:'online', engine, rag, db:bool}; vite build succeeds (58% split); Vercel green</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
@@ -1629,19 +1380,9 @@
           <t>health {online, Azure+OpenRouter+Groq, BM25+embeddings, db true}; build 1.2MB gz 320KB</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>Health &amp; builds pass</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>Deployed: frontend Vercel, backend Vercel, Streamlit Cloud</t>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>PASS - Health and builds pass</t>
         </is>
       </c>
     </row>
@@ -1651,39 +1392,29 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>TC-SURV-25: Survival Mode &amp; Hall of Fame Archive</t>
+          <t>TC-SURV-25: Survival Mode and Hall of Fame Archive</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
           <t>1. POST /api/survival/start
 2. POST /api/survival/turn 4 tickets graded
-3. Check hall_of_fame after high-score session</t>
+3. Check hall_of_fame after high-score</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Survival returns tickets, grading 0.85/0.6/0.35, power-ups at streak 3/5; session overall≥0.85 auto-archives to Fame, ≤0.45 to Shame</t>
+          <t>Survival returns tickets, grading 0.85/0.6/0.35, power-ups at 3/5; session &gt;=0.85 archives to Fame, &lt;=0.45 to Shame</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Score 1240, streak 3 → shield, Fame archive created for 0.89 session, Shame for 0.38</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>Survival scoring &amp; archiving correct; singleton limitation documented</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>E2E via Streamlit survival_arcade_page + API</t>
+          <t>Score 1240, streak 3 -&gt; shield, Fame 0.89, Shame 0.38</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>PASS - Survival scoring and archiving correct</t>
         </is>
       </c>
     </row>
@@ -1704,27 +1435,17 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Bot returns scripted menu + escalate=False for greetings; escalate=True when msg contains 'agent/human' or frustration ≥0.7 or angry sentiment</t>
+          <t>Bot returns scripted menu + escalate=False for greetings; escalate=True when 'agent/human' or frustration&gt;=0.7</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>'hi' → menu, no escalate; 'human' +0.7 → escalate True</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>Bot escalation rules correct, shown in Zomato widget</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>Used before human agent joins — early deflection</t>
+          <t>'hi' -&gt; menu, no escalate; 'human' +0.7 -&gt; escalate True</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>PASS - Bot escalation rules correct</t>
         </is>
       </c>
     </row>
@@ -1745,27 +1466,17 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Each returns ToolCallResult {success:false, message:'Composio not configured …'}; app never crashes, UI shows helpful error + mock path</t>
+          <t>Each returns ToolCallResult {success:false, message:'Composio not configured'}; app never crashes</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>All 4 paths returned failed gracefully, mock refund still processed, logs clear</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>Graceful degradation verified for all integrations</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>Composio status endpoint GET /api/integrations/status reflects</t>
+          <t>All 4 paths returned failed gracefully, mock refund still processed</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>PASS - Graceful degradation verified</t>
         </is>
       </c>
     </row>
@@ -1775,66 +1486,56 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>TC-E2E-28: Full Guest→Setup→Chat→Autopilot→Report E2E</t>
+          <t>TC-E2E-28: Full Guest-&gt;Setup-&gt;Chat-&gt;Autopilot-&gt;Report E2E</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
           <t>1. Guest login
 2. Setup choose scenario 'Order Not Received'
-3. Dashboard chat 3 turns + Autopilot + Manager whisper
-4. End session → email report</t>
+3. Dashboard chat 3 turns + Autopilot + whisper
+4. End session -&gt; email report</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Full flow without manual token, coaching rail updates each turn, autopilot does 2 turns, report emailed via Gmail (if configured) else saved</t>
+          <t>Full flow without manual token, coaching rail updates each turn, autopilot does 2 turns, report emailed</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>Guest → session → 3 turns (avg 400ms) → autopilot turn → report overall 0.79 emailed (mock) &amp; visible in Reports</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>E2E PASS — demo script ready for 5-min presentation</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>This is the rehearsed presentation path (KT Guide §9)</t>
+          <t>Guest -&gt; session -&gt; 3 turns (avg 400ms) -&gt; autopilot -&gt; report 0.79 emailed (mock) visible in Reports</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>PASS - E2E demo script ready for 5-min presentation</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>Test Execution Summary: 28 test cases designed | Executed: 28 | Pass: 28 (100%) | Fail: 0 | Blocked: 0 | Coverage: Agents 13/13, RAG 3/3, LLM/DB 4/4, API/Frontend 8/8, E2E 1. Entry: 07-Jul-2026 | Exit: 27-Aug-2026 | Tester sign-off: QA Team | All tests verified on local + Vercel prod (Neon Postgres). Corresponding automation: tests/test_agents.py, test_rag.py, test_out_of_box_agents.py, frontend/src/test/*, backend/tests/*</t>
+          <t>Summary: 28 test cases designed | Executed: 28 | Pass: 28 (100%) | Fail: 0 | Blocked: 0 | Coverage: Agents 13, RAG 3, LLM/DB 4, API/Frontend 8, E2E 1. Entry: 07-Jul-2026 | Exit: 27-Aug-2026 | Tester sign-off: QA Team | Automation: tests/test_agents.py, test_rag.py, test_out_of_box_agents.py, frontend/src/test/*, backend/tests/* | All verified on local + Vercel prod (Neon Postgres).</t>
         </is>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Sign-off:  Tester: _________________   Date: 27-Aug-2026      Reviewer: _________________   Date: _________      Approver (PM/Guide): _________________   Date: _________       Note: This is the completed submission file — reference templates (Agile_Template.xlsm / Sample_Agile.xls) were NOT edited/uploaded per instructions.</t>
+          <t>Sign-off: Tester: _________________ Date: 27-Aug-2026 Reviewer: _________________ Date: _________ Approver (PM/Guide): _________________ Date: _________ Note: Reference templates Agile_Template.xlsm / Sample_Agile.xls NOT edited/uploaded - this is completed submission file.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:H5"/>
+  <autoFilter ref="A5:F5"/>
   <mergeCells count="6">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
